--- a/data/trans_camb/BARTHEL_R2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/BARTHEL_R2-Edad-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel)</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,04</t>
+          <t>2,76</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,86</t>
+          <t>1,12</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>1,83</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 8,08</t>
+          <t>0,79; 8,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 5,8</t>
+          <t>-0,72; 5,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 5,77</t>
+          <t>0,02; 5,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 9,2</t>
+          <t>0,77; 10,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 6,33</t>
+          <t>-2,49; 5,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 1,68</t>
+          <t>-2,32; 4,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 7,55</t>
+          <t>1,58; 7,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 4,56</t>
+          <t>-0,58; 4,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 2,77</t>
+          <t>-0,54; 3,79</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-26,37%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>33,82%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,27; 399,63</t>
+          <t>8,5; 357,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-20,11; 288,54</t>
+          <t>-21,25; 243,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 274,79</t>
+          <t>-2,16; 274,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 176,71</t>
+          <t>6,37; 198,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-22,38; 122,13</t>
+          <t>-28,26; 114,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-76,0; 24,54</t>
+          <t>-24,4; 90,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,73; 172,44</t>
+          <t>22,68; 185,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 112,19</t>
+          <t>-10,86; 123,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-50,43; 60,39</t>
+          <t>-8,92; 90,78</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,66</t>
+          <t>6,99</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,07</t>
+          <t>17,06</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>13,24</t>
+          <t>12,95</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,31; 17,28</t>
+          <t>2,16; 17,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 12,29</t>
+          <t>-1,38; 11,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 13,97</t>
+          <t>0,66; 12,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,23; 25,14</t>
+          <t>12,13; 26,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,78; 21,02</t>
+          <t>6,37; 20,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,26; 23,18</t>
+          <t>11,51; 22,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,09; 20,06</t>
+          <t>9,95; 20,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,93; 15,41</t>
+          <t>5,26; 15,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,15; 17,69</t>
+          <t>8,22; 17,03</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>72,93%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,18; 146,88</t>
+          <t>11,01; 166,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 119,23</t>
+          <t>-8,53; 107,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,09; 133,11</t>
+          <t>1,99; 117,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49,08; 152,91</t>
+          <t>52,22; 158,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,93; 127,64</t>
+          <t>26,63; 122,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,48; 144,67</t>
+          <t>46,1; 141,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,77; 130,18</t>
+          <t>47,64; 135,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28,69; 99,99</t>
+          <t>24,69; 103,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>42,86; 118,07</t>
+          <t>38,59; 113,63</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,19</t>
+          <t>4,71</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,84</t>
+          <t>9,57</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,19</t>
+          <t>7,32</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,99; 10,37</t>
+          <t>3,09; 10,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 7,05</t>
+          <t>0,53; 7,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,11; 8,34</t>
+          <t>1,52; 7,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,25; 16,95</t>
+          <t>8,12; 16,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,06; 12,52</t>
+          <t>3,89; 12,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 10,56</t>
+          <t>6,37; 13,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,18; 12,99</t>
+          <t>7,09; 13,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,66; 9,1</t>
+          <t>3,59; 9,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 8,36</t>
+          <t>4,71; 9,86</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>65,9%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30,18; 167,72</t>
+          <t>30,64; 168,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,59; 107,08</t>
+          <t>5,34; 115,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18,31; 127,91</t>
+          <t>14,8; 125,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53,01; 148,31</t>
+          <t>50,61; 147,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24,72; 107,54</t>
+          <t>24,13; 110,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-28,38; 85,25</t>
+          <t>41,06; 118,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>57,68; 133,08</t>
+          <t>56,37; 133,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30,0; 94,43</t>
+          <t>29,49; 93,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 83,15</t>
+          <t>35,19; 101,31</t>
         </is>
       </c>
     </row>
